--- a/data/trans_orig/IP25B_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25B_1_R-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30606</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>53399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67340</t>
+          <t>67533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61058</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73243</t>
+          <t>73148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121571</t>
+          <t>121139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138766</t>
+          <t>138459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>40090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91392</t>
+          <t>92433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37696</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60952</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88407</t>
+          <t>87758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157720</t>
+          <t>155368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33841</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84546</t>
+          <t>85143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65878</t>
+          <t>64986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89134</t>
+          <t>88496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94343</t>
+          <t>96695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163656</t>
+          <t>164305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38213</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>48017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>46483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57555</t>
+          <t>58072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86822</t>
+          <t>86767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>102845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44133</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58778</t>
+          <t>60302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58785</t>
+          <t>58488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63113</t>
+          <t>62447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81598</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119046</t>
+          <t>117443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59905</t>
+          <t>59991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70507</t>
+          <t>70918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38788</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49390</t>
+          <t>49184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71063</t>
+          <t>71259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>84589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37384</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63912</t>
+          <t>65182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67501</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102072</t>
+          <t>99847</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78497</t>
+          <t>77734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94679</t>
+          <t>94039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88834</t>
+          <t>87564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115362</t>
+          <t>114782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>169897</t>
+          <t>172122</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>204468</t>
+          <t>204396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45104</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103186</t>
+          <t>104391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>118410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132732</t>
+          <t>132434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>145722</t>
+          <t>146024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>241746</t>
+          <t>241363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>262243</t>
+          <t>261617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132180</t>
+          <t>131679</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>228954</t>
+          <t>231542</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>156383</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>214708</t>
+          <t>216130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>305178</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>420889</t>
+          <t>417915</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>422040</t>
+          <t>419452</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>518814</t>
+          <t>519315</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>540352</t>
+          <t>538930</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>598677</t>
+          <t>597368</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>985166</t>
+          <t>988140</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1100877</t>
+          <t>1099311</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
